--- a/OUTPUT/RealizeReports/Nowshin.xlsx
+++ b/OUTPUT/RealizeReports/Nowshin.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Nowshin" displayName="Nowshin" ref="A1:Y77" headerRowCount="1">
-  <autoFilter ref="A1:Y77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Nowshin" displayName="Nowshin" ref="A1:Y75" headerRowCount="1">
+  <autoFilter ref="A1:Y75"/>
   <tableColumns count="25">
     <tableColumn id="1" name="SL"/>
     <tableColumn id="2" name="LC_Factory"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4004</v>
+        <v>41449</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Auric Sourcing BD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2310036</t>
+          <t>2411147</t>
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45034</v>
+        <v>45500</v>
       </c>
       <c r="G2" t="n">
-        <v>500</v>
+        <v>1033</v>
       </c>
       <c r="H2" t="n">
-        <v>4128</v>
+        <v>4583.65</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>500</v>
+        <v>1033</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>45034.45460648148</v>
+        <v>45516.35745370371</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>45046</v>
+        <v>45537</v>
       </c>
       <c r="M2" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -678,11 +678,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1647/23</t>
+          <t>FDC-2689</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>45057</v>
+        <v>45519</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -705,53 +705,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>35163</v>
+        <v>15566</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Auric Sourcing BD</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2411200</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>45501</v>
+      </c>
+      <c r="G3" t="n">
+        <v>152</v>
+      </c>
+      <c r="H3" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>MFSL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sweater</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hellenic Trading AB</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2310069</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>45036</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7550</v>
-      </c>
-      <c r="H3" t="n">
-        <v>42909.25</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
       <c r="J3" t="n">
-        <v>7550</v>
+        <v>152</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>45037.60773148148</v>
+        <v>45516.35745370371</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>45068</v>
+        <v>45519</v>
       </c>
       <c r="M3" t="n">
-        <v>231.75</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -763,21 +763,21 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Felixtowe</t>
+          <t>KAZAKHSTAN</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>FDBC/0471/23</t>
+          <t>FDC2688</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>45074</v>
+        <v>45519</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>39107</v>
+        <v>10315</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -814,22 +814,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WEATHERPROOF VINTAGE</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2310067</t>
+          <t>2411802</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45069</v>
+        <v>45512</v>
       </c>
       <c r="G4" t="n">
-        <v>9840</v>
+        <v>2107</v>
       </c>
       <c r="H4" t="n">
-        <v>68388</v>
+        <v>12027.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9420</v>
+        <v>2007</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>45097.83900462963</v>
+        <v>45512.77430555555</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>45092</v>
+        <v>45528</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -853,12 +853,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Sea/Air</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -868,11 +868,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>FDBC-2429/23</t>
+          <t>3318/24</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>45131</v>
+        <v>45558</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35216</v>
+        <v>13181</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -909,22 +909,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WEATHERPROOF VINTAGE</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2310494</t>
+          <t>2411945</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45098</v>
+        <v>45515</v>
       </c>
       <c r="G5" t="n">
-        <v>12306</v>
+        <v>5511</v>
       </c>
       <c r="H5" t="n">
-        <v>85526.7</v>
+        <v>35862.83</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -932,28 +932,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2886</v>
+        <v>5511</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>45097.79877314815</v>
+        <v>45522.37118055556</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>45103</v>
+        <v>45536</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1887.52</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Sea/Air</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -963,11 +963,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>FDBC-2429/23</t>
+          <t>3166/24</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>45131</v>
+        <v>45552</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -990,11 +990,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>38160</v>
+        <v>28424</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1004,22 +1004,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Street One</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2310864</t>
+          <t>2412017</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45113</v>
+        <v>45518</v>
       </c>
       <c r="G6" t="n">
-        <v>18989</v>
+        <v>20248</v>
       </c>
       <c r="H6" t="n">
-        <v>126846.28</v>
+        <v>131599.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1027,16 +1027,16 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18989</v>
+        <v>20248</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>45083.86256944444</v>
+        <v>45518.76497685185</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>45087</v>
+        <v>45527</v>
       </c>
       <c r="M6" t="n">
-        <v>380.02</v>
+        <v>6926.28</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1048,21 +1048,21 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>FDBC/1221/23</t>
+          <t>3166/24</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>45098</v>
+        <v>45552</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,11 +1085,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>33449</v>
+        <v>31476</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Street One</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2310863</t>
+          <t>2412270</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>45113</v>
+        <v>45524</v>
       </c>
       <c r="G7" t="n">
-        <v>8170</v>
+        <v>4718</v>
       </c>
       <c r="H7" t="n">
-        <v>54739</v>
+        <v>29492.22</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1122,42 +1122,42 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8170</v>
+        <v>4718</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>45083.85983796296</v>
+        <v>45545.45666666667</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>45093</v>
+        <v>45547</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1552.22</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>FDBC/1221/23</t>
+          <t>3319/24</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>45098</v>
+        <v>45561</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1180,11 +1180,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>46270</v>
+        <v>42001</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,39 +1194,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Street One</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2313197</t>
+          <t>2412586</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>45117</v>
+        <v>45533</v>
       </c>
       <c r="G8" t="n">
-        <v>37237</v>
+        <v>570</v>
       </c>
       <c r="H8" t="n">
-        <v>286724.9</v>
+        <v>3221.92</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>37237</v>
+        <v>570</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>45130.62752314815</v>
+        <v>45532.47994212963</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>45137</v>
+        <v>45542</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>169.58</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1238,21 +1238,21 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>FDBP/1507/23</t>
+          <t>3319/24</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>44965</v>
+        <v>45561</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1275,11 +1275,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>23989</v>
+        <v>30890</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1289,39 +1289,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Street One</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2313198</t>
+          <t>2412745</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45118</v>
+        <v>45535</v>
       </c>
       <c r="G9" t="n">
-        <v>10090</v>
+        <v>6680</v>
       </c>
       <c r="H9" t="n">
-        <v>77693</v>
+        <v>43470.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10090</v>
+        <v>6680</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>45131.62981481481</v>
+        <v>45533.53450231482</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>45137</v>
+        <v>45542</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2287.9</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1333,21 +1333,21 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>FDBP/1507/23</t>
+          <t>3319/24</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>44965</v>
+        <v>45561</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>41479</v>
+        <v>27298</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1384,39 +1384,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2312572</t>
+          <t>2412874</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45162</v>
+        <v>45536</v>
       </c>
       <c r="G10" t="n">
-        <v>14224</v>
+        <v>851</v>
       </c>
       <c r="H10" t="n">
-        <v>91373.58</v>
+        <v>6808</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14224</v>
+        <v>851</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>45462.84813657407</v>
+        <v>45540.7222800926</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>45102</v>
+        <v>45549</v>
       </c>
       <c r="M10" t="n">
-        <v>513.46</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1428,21 +1428,21 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>FDBC/0589/2023</t>
+          <t>2261/24</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>45112</v>
+        <v>45559</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1465,53 +1465,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48381</v>
+        <v>28776</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BSI APPAREL LTD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2412924</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>45539</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10489</v>
+      </c>
+      <c r="H11" t="n">
+        <v>69809.89</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>MFSL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sweater</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DK Company</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2313472</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>45189</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1539</v>
-      </c>
-      <c r="H11" t="n">
-        <v>15836.65</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
       <c r="J11" t="n">
-        <v>1539</v>
+        <v>10489</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>45188.70141203704</v>
+        <v>45540.71069444445</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>45195</v>
+        <v>45550</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2999.76</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1523,21 +1523,21 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>934/23</t>
+          <t>69809.65</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>45203</v>
+        <v>45561</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>32287</v>
+        <v>28894</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1574,22 +1574,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2313471</t>
+          <t>2413872</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>45189</v>
+        <v>45556</v>
       </c>
       <c r="G12" t="n">
-        <v>389</v>
+        <v>21180</v>
       </c>
       <c r="H12" t="n">
-        <v>3872.05</v>
+        <v>41168.66</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>389</v>
+        <v>21180</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>45188.57975694445</v>
+        <v>45592.36891203704</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>45195</v>
+        <v>45606</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3309.34</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>934/23</t>
+          <t>$122722.40</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>45203</v>
+        <v>45641</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>400</v>
+        <v>42494</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1669,39 +1669,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kariban</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2313901</t>
+          <t>2413871</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>45195</v>
+        <v>45556</v>
       </c>
       <c r="G13" t="n">
-        <v>8580</v>
+        <v>20880</v>
       </c>
       <c r="H13" t="n">
-        <v>51909</v>
+        <v>44561.32</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8580</v>
+        <v>20880</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>45209.73105324074</v>
+        <v>45591.42358796296</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>45201</v>
+        <v>45597</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3462.68</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1713,21 +1713,21 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>FDBC/997/23</t>
+          <t>$122722.40</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>45224</v>
+        <v>45641</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1750,53 +1750,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>34769</v>
+        <v>17107</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AAMARA TEX LTD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2414546</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4134</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24846</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>MFSL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sweater</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Hellenic Trading AB</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2315555</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>45232</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14380</v>
-      </c>
-      <c r="H14" t="n">
-        <v>32421.58</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
       <c r="J14" t="n">
-        <v>14380</v>
+        <v>4134</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>45290.36759259259</v>
+        <v>45568.66247685185</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>45302</v>
+        <v>45576</v>
       </c>
       <c r="M14" t="n">
-        <v>652.42</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1808,21 +1808,21 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>FDBC-82/24</t>
+          <t>54,184.80</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>45308</v>
+        <v>45624</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1845,53 +1845,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8410</v>
+        <v>2946</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AAMARA TEX LTD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2414532</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4896</v>
+      </c>
+      <c r="H15" t="n">
+        <v>29338.8</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>MFSL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Sweater</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Hellenic Trading AB</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2316015</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>45244</v>
-      </c>
-      <c r="G15" t="n">
-        <v>21284</v>
-      </c>
-      <c r="H15" t="n">
-        <v>69531.05</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
       <c r="J15" t="n">
-        <v>21284</v>
+        <v>4896</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>45288.41481481482</v>
+        <v>45568.65729166667</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>45302</v>
+        <v>45576</v>
       </c>
       <c r="M15" t="n">
-        <v>9219.75</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Felixtowe</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>083-24</t>
+          <t>54,184.80</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>45308</v>
+        <v>45624</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40143</v>
+        <v>339</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1954,39 +1954,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ZXY</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2316605</t>
+          <t>2414982</t>
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>45252</v>
+        <v>45577</v>
       </c>
       <c r="G16" t="n">
-        <v>6072</v>
+        <v>30168</v>
       </c>
       <c r="H16" t="n">
-        <v>30432.17</v>
+        <v>115847.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6072</v>
+        <v>30168</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>45252.45554398148</v>
+        <v>45614.55766203703</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>45262</v>
+        <v>45617</v>
       </c>
       <c r="M16" t="n">
-        <v>4530.01</v>
+        <v>1807.3</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2008,11 +2008,11 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2522/23</t>
+          <t>$115847.87</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>45273</v>
+        <v>45643</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>42900</v>
+        <v>4261</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2049,51 +2049,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hellenic Trading AB</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2317394</t>
+          <t>2415532</t>
         </is>
       </c>
       <c r="F17" s="1" t="n">
-        <v>45265</v>
+        <v>45589</v>
       </c>
       <c r="G17" t="n">
-        <v>21596</v>
+        <v>4218</v>
       </c>
       <c r="H17" t="n">
-        <v>50902.57</v>
+        <v>18348.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>21596</v>
+        <v>4218</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>45311.37347222222</v>
+        <v>45588.67109953704</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>45319</v>
+        <v>45584</v>
       </c>
       <c r="M17" t="n">
-        <v>6326.83</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2103,11 +2103,11 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>FDBC-0456/24</t>
+          <t>$18348.30</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>45334</v>
+        <v>45609</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2130,11 +2130,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>39510</v>
+        <v>14296</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2144,36 +2144,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Auric Sourcing BD</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2411147</t>
+          <t>2415704</t>
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>45500</v>
+        <v>45591</v>
       </c>
       <c r="G18" t="n">
-        <v>1033</v>
+        <v>6174</v>
       </c>
       <c r="H18" t="n">
-        <v>4583.65</v>
+        <v>26856.9</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1033</v>
+        <v>6174</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>45516.35745370371</v>
+        <v>45592.48755787037</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>45537</v>
+        <v>45597</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2183,26 +2183,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>FDC-2689</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>45519</v>
+        <v>45739</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,11 +2225,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31776</v>
+        <v>27251</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Auric Sourcing BD</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2411200</t>
+          <t>2415858</t>
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45501</v>
+        <v>45594</v>
       </c>
       <c r="G19" t="n">
-        <v>152</v>
+        <v>17560</v>
       </c>
       <c r="H19" t="n">
-        <v>676.4</v>
+        <v>36992.46</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2262,16 +2262,16 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>152</v>
+        <v>17560</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>45516.35745370371</v>
+        <v>45593.44770833333</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>45519</v>
+        <v>45608</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3395.54</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2283,21 +2283,21 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>KAZAKHSTAN</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>FDC2688</t>
+          <t>$122722.40</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>45519</v>
+        <v>45641</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2320,11 +2320,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13529</v>
+        <v>26125</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2339,17 +2339,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2411802</t>
+          <t>2416908</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>45512</v>
+        <v>45615</v>
       </c>
       <c r="G20" t="n">
-        <v>2107</v>
+        <v>2002</v>
       </c>
       <c r="H20" t="n">
-        <v>12027.6</v>
+        <v>8708.700000000001</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>45512.77430555555</v>
+        <v>45617.68335648148</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>45528</v>
+        <v>45617</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2373,26 +2373,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sea/Air</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>3318/24</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>45558</v>
+        <v>45739</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2415,11 +2415,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22004</v>
+        <v>13700</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2429,22 +2429,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2411945</t>
+          <t>2416909</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>45515</v>
+        <v>45615</v>
       </c>
       <c r="G21" t="n">
-        <v>5511</v>
+        <v>2002</v>
       </c>
       <c r="H21" t="n">
-        <v>35862.83</v>
+        <v>8708.700000000001</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2452,42 +2452,42 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5511</v>
+        <v>2002</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>45522.37118055556</v>
+        <v>45617.67180555555</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>45536</v>
+        <v>45617</v>
       </c>
       <c r="M21" t="n">
-        <v>1887.52</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sea/Air</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>3166/24</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>45552</v>
+        <v>45739</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2510,11 +2510,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>15567</v>
+        <v>14624</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2412017</t>
+          <t>2416910</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>45518</v>
+        <v>45615</v>
       </c>
       <c r="G22" t="n">
-        <v>20248</v>
+        <v>2002</v>
       </c>
       <c r="H22" t="n">
-        <v>131599.32</v>
+        <v>8708.700000000001</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2547,42 +2547,42 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>20248</v>
+        <v>2002</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>45518.76497685185</v>
+        <v>45617.67793981481</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>45527</v>
+        <v>45617</v>
       </c>
       <c r="M22" t="n">
-        <v>6926.28</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>3166/24</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>45552</v>
+        <v>45739</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2605,11 +2605,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11564</v>
+        <v>2509</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2619,22 +2619,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2412270</t>
+          <t>2416907</t>
         </is>
       </c>
       <c r="F23" s="1" t="n">
-        <v>45524</v>
+        <v>45615</v>
       </c>
       <c r="G23" t="n">
-        <v>4718</v>
+        <v>2002</v>
       </c>
       <c r="H23" t="n">
-        <v>29492.22</v>
+        <v>8708.700000000001</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2642,16 +2642,16 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4718</v>
+        <v>2002</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>45545.45666666667</v>
+        <v>45617.67793981481</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>45547</v>
+        <v>45617</v>
       </c>
       <c r="M23" t="n">
-        <v>1552.22</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2663,21 +2663,21 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>3319/24</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>45561</v>
+        <v>45739</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2700,11 +2700,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>43073</v>
+        <v>18190</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2412586</t>
+          <t>2416906</t>
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>45533</v>
+        <v>45615</v>
       </c>
       <c r="G24" t="n">
-        <v>570</v>
+        <v>2028</v>
       </c>
       <c r="H24" t="n">
-        <v>3221.92</v>
+        <v>8821.799999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2737,42 +2737,42 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>570</v>
+        <v>2028</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>45532.47994212963</v>
+        <v>45617.68335648148</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>45542</v>
+        <v>45617</v>
       </c>
       <c r="M24" t="n">
-        <v>169.58</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3319/24</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>45561</v>
+        <v>45739</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2795,11 +2795,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>39766</v>
+        <v>10849</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2809,22 +2809,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2412745</t>
+          <t>2416911</t>
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>45535</v>
+        <v>45615</v>
       </c>
       <c r="G25" t="n">
-        <v>6680</v>
+        <v>2002</v>
       </c>
       <c r="H25" t="n">
-        <v>43470.1</v>
+        <v>8708.700000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2832,42 +2832,42 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6680</v>
+        <v>2002</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>45533.53450231482</v>
+        <v>45617.67180555555</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>45542</v>
+        <v>45617</v>
       </c>
       <c r="M25" t="n">
-        <v>2287.9</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>3319/24</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>45561</v>
+        <v>45739</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2890,11 +2890,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51802</v>
+        <v>22603</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2904,36 +2904,36 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TMS Fashion (HK) Ltd.</t>
+          <t>Michael Kors (USA), Inc.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2412874</t>
+          <t>2604775</t>
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>45536</v>
+        <v>46141</v>
       </c>
       <c r="G26" t="n">
-        <v>851</v>
+        <v>24240</v>
       </c>
       <c r="H26" t="n">
-        <v>6808</v>
+        <v>150772.8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>851</v>
+        <v>24240</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>45540.7222800926</v>
+        <v>46160.52238425926</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>45549</v>
+        <v>46167</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2948,21 +2948,21 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2261/24</t>
+          <t>2052/2026</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>45559</v>
+        <v>46177</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>46220</v>
+        <v>19205</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2999,39 +2999,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BSI APPAREL LTD</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2412924</t>
+          <t>2605751</t>
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>45539</v>
+        <v>46160</v>
       </c>
       <c r="G27" t="n">
-        <v>10489</v>
+        <v>693</v>
       </c>
       <c r="H27" t="n">
-        <v>69809.89</v>
+        <v>4097.48</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>10489</v>
+        <v>693</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>45540.71069444445</v>
+        <v>46271.53631944444</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>45550</v>
+        <v>46284</v>
       </c>
       <c r="M27" t="n">
-        <v>2999.76</v>
+        <v>83.62</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Jabel-Ali</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3053,11 +3053,11 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>69809.65</t>
+          <t>52958.59</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>45561</v>
+        <v>46287</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3080,11 +3080,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29668</v>
+        <v>24425</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3094,39 +3094,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2413871</t>
+          <t>2605750</t>
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>45556</v>
+        <v>46160</v>
       </c>
       <c r="G28" t="n">
-        <v>20880</v>
+        <v>14010</v>
       </c>
       <c r="H28" t="n">
-        <v>44561.32</v>
+        <v>74650.52</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>20880</v>
+        <v>18456</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>45591.42358796296</v>
+        <v>46161</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>45597</v>
+        <v>46184</v>
       </c>
       <c r="M28" t="n">
-        <v>3462.68</v>
+        <v>1523.48</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3138,21 +3138,21 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>$122722.40</t>
+          <t>98178.75</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>45641</v>
+        <v>46222</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>39288</v>
+        <v>38158</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3189,22 +3189,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2413872</t>
+          <t>2606111</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>45556</v>
+        <v>46165</v>
       </c>
       <c r="G29" t="n">
-        <v>21180</v>
+        <v>1282</v>
       </c>
       <c r="H29" t="n">
-        <v>41168.66</v>
+        <v>4847.14</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3212,28 +3212,28 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>21180</v>
+        <v>1282</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>45592.36891203704</v>
+        <v>46196.4912962963</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>45606</v>
+        <v>46204</v>
       </c>
       <c r="M29" t="n">
-        <v>3309.34</v>
+        <v>5651.36</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3243,11 +3243,11 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>$122722.40</t>
+          <t>1174/26</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>45641</v>
+        <v>46212</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3270,11 +3270,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8375</v>
+        <v>33404</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3284,22 +3284,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AAMARA TEX LTD</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2414532</t>
+          <t>2606112</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>45568</v>
+        <v>46165</v>
       </c>
       <c r="G30" t="n">
-        <v>4896</v>
+        <v>2734</v>
       </c>
       <c r="H30" t="n">
-        <v>29338.8</v>
+        <v>20769.3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4896</v>
+        <v>2734</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>45568.65729166667</v>
+        <v>46188.69032407407</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>45576</v>
+        <v>46196</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3323,26 +3323,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Felixtowe</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>54,184.80</t>
+          <t>1180/26</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>45624</v>
+        <v>46217</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>40822</v>
+        <v>16439</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3379,51 +3379,51 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AAMARA TEX LTD</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2414546</t>
+          <t>2606424</t>
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>45568</v>
+        <v>46180</v>
       </c>
       <c r="G31" t="n">
-        <v>4134</v>
+        <v>3570</v>
       </c>
       <c r="H31" t="n">
-        <v>24846</v>
+        <v>17562.96</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4134</v>
+        <v>3570</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>45568.66247685185</v>
+        <v>46231.41276620371</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>45576</v>
+        <v>46238</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>11708.64</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3433,11 +3433,11 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>54,184.80</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>45624</v>
+        <v>46271</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3460,11 +3460,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>24525</v>
+        <v>34076</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3474,39 +3474,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>ONLY RETAIL PRIVATE LIMITED.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2414982</t>
+          <t>2606588</t>
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>45577</v>
+        <v>46187</v>
       </c>
       <c r="G32" t="n">
-        <v>30168</v>
+        <v>1476</v>
       </c>
       <c r="H32" t="n">
-        <v>115847.9</v>
+        <v>10346.76</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>30168</v>
+        <v>1476</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>45614.55766203703</v>
+        <v>46210.38983796296</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>45617</v>
+        <v>46217</v>
       </c>
       <c r="M32" t="n">
-        <v>1807.3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3518,21 +3518,21 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>India</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>$115847.87</t>
+          <t>10346.76</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>45643</v>
+        <v>46231</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>42167</v>
+        <v>25795</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3569,39 +3569,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2415532</t>
+          <t>2606660</t>
         </is>
       </c>
       <c r="F33" s="1" t="n">
-        <v>45589</v>
+        <v>46188</v>
       </c>
       <c r="G33" t="n">
-        <v>4218</v>
+        <v>2408</v>
       </c>
       <c r="H33" t="n">
-        <v>18348.3</v>
+        <v>15185.99</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>4218</v>
+        <v>2408</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>45588.67109953704</v>
+        <v>46196.49310185185</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>45584</v>
+        <v>46199</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4230.01</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3623,11 +3623,11 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>$18348.30</t>
+          <t>1174/26</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>45609</v>
+        <v>46212</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>45198</v>
+        <v>5308</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3664,39 +3664,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2415704</t>
+          <t>2606661</t>
         </is>
       </c>
       <c r="F34" s="1" t="n">
-        <v>45591</v>
+        <v>46188</v>
       </c>
       <c r="G34" t="n">
-        <v>6174</v>
+        <v>509</v>
       </c>
       <c r="H34" t="n">
-        <v>26856.9</v>
+        <v>2670.16</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>6174</v>
+        <v>509</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>45592.48755787037</v>
+        <v>46196.4912962963</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>45597</v>
+        <v>46205</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1427.34</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3718,11 +3718,11 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>1174/26</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>45739</v>
+        <v>46212</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>21911</v>
+        <v>40912</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3759,22 +3759,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2415858</t>
+          <t>2606676</t>
         </is>
       </c>
       <c r="F35" s="1" t="n">
-        <v>45594</v>
+        <v>46190</v>
       </c>
       <c r="G35" t="n">
-        <v>17560</v>
+        <v>2390</v>
       </c>
       <c r="H35" t="n">
-        <v>36992.46</v>
+        <v>27531.01</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3782,28 +3782,28 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>17560</v>
+        <v>2390</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>45593.44770833333</v>
+        <v>46216.59604166666</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>45608</v>
+        <v>46221</v>
       </c>
       <c r="M35" t="n">
-        <v>3395.54</v>
+        <v>3121.19</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3813,11 +3813,11 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>$122722.40</t>
+          <t>1216/26</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>45641</v>
+        <v>46225</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>27529</v>
+        <v>34101</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3854,39 +3854,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2416908</t>
+          <t>2606677</t>
         </is>
       </c>
       <c r="F36" s="1" t="n">
-        <v>45615</v>
+        <v>46190</v>
       </c>
       <c r="G36" t="n">
-        <v>2002</v>
+        <v>1428</v>
       </c>
       <c r="H36" t="n">
-        <v>8708.700000000001</v>
+        <v>14550.86</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>2002</v>
+        <v>1428</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>45617.68335648148</v>
+        <v>46216.59912037037</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>45617</v>
+        <v>46218</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2688.64</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>1216/26</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>45739</v>
+        <v>46225</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48891</v>
+        <v>1890</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3949,39 +3949,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2416909</t>
+          <t>2607031</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>45615</v>
+        <v>46195</v>
       </c>
       <c r="G37" t="n">
-        <v>2002</v>
+        <v>630</v>
       </c>
       <c r="H37" t="n">
-        <v>8708.700000000001</v>
+        <v>6661.87</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2002</v>
+        <v>630</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>45617.67180555555</v>
+        <v>46197.73806712963</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>45617</v>
+        <v>46204</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1181.63</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4003,11 +4003,11 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>1174/26</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>45739</v>
+        <v>46212</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>23242</v>
+        <v>31862</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4044,39 +4044,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2416906</t>
+          <t>2607032</t>
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>45615</v>
+        <v>46195</v>
       </c>
       <c r="G38" t="n">
-        <v>2028</v>
+        <v>1240</v>
       </c>
       <c r="H38" t="n">
-        <v>8821.799999999999</v>
+        <v>13963.79</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>2028</v>
+        <v>1240</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>45617.68335648148</v>
+        <v>46197.74751157407</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>45617</v>
+        <v>46201</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1474.21</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4098,11 +4098,11 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>1180/26</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>45739</v>
+        <v>46217</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4125,11 +4125,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>32292</v>
+        <v>27408</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4139,22 +4139,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2416907</t>
+          <t>2607070</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>45615</v>
+        <v>46197</v>
       </c>
       <c r="G39" t="n">
-        <v>2002</v>
+        <v>2301</v>
       </c>
       <c r="H39" t="n">
-        <v>8708.700000000001</v>
+        <v>13575.9</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>2002</v>
+        <v>2365</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>45617.67793981481</v>
+        <v>46197.37570601852</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>45617</v>
+        <v>46201</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4178,26 +4178,26 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>27529.40</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>45739</v>
+        <v>46212</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4220,11 +4220,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10053</v>
+        <v>3119</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4234,22 +4234,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2416911</t>
+          <t>2607069</t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>45615</v>
+        <v>46197</v>
       </c>
       <c r="G40" t="n">
-        <v>2002</v>
+        <v>2365</v>
       </c>
       <c r="H40" t="n">
-        <v>8708.700000000001</v>
+        <v>13953.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2002</v>
+        <v>2301</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>45617.67180555555</v>
+        <v>46197.37570601852</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>45617</v>
+        <v>46201</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4273,26 +4273,26 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>27529.40</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>45739</v>
+        <v>46212</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4315,11 +4315,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>16514</v>
+        <v>17669</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4329,22 +4329,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2416910</t>
+          <t>2607448</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
-        <v>45615</v>
+        <v>46204</v>
       </c>
       <c r="G41" t="n">
-        <v>2002</v>
+        <v>1450</v>
       </c>
       <c r="H41" t="n">
-        <v>8708.700000000001</v>
+        <v>9526.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4352,42 +4352,42 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>2002</v>
+        <v>1450</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>45617.67793981481</v>
+        <v>46205.38795138889</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>45617</v>
+        <v>46216</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1058.5</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>21370.50</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>45739</v>
+        <v>46222</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6826</v>
+        <v>19313</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4424,22 +4424,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Michael Kors (USA), Inc.</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2604775</t>
+          <t>2607449</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>46141</v>
+        <v>46204</v>
       </c>
       <c r="G42" t="n">
-        <v>24240</v>
+        <v>1880</v>
       </c>
       <c r="H42" t="n">
-        <v>150772.8</v>
+        <v>11844</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>24240</v>
+        <v>1880</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46160.52238425926</v>
+        <v>46205.38795138889</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>46167</v>
+        <v>46216</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4478,11 +4478,11 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2052/2026</t>
+          <t>21370.50</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>46177</v>
+        <v>46222</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4505,11 +4505,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>35721</v>
+        <v>29251</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4519,65 +4519,65 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2605750</t>
+          <t>2607546</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46160</v>
+        <v>46205</v>
       </c>
       <c r="G43" t="n">
-        <v>14010</v>
+        <v>400</v>
       </c>
       <c r="H43" t="n">
-        <v>74650.52</v>
+        <v>2350</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>18456</v>
+        <v>400</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46161</v>
+        <v>46219.46043981481</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46184</v>
+        <v>46223</v>
       </c>
       <c r="M43" t="n">
-        <v>1523.48</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>98178.75</t>
+          <t>1296/26</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>46222</v>
+        <v>46237</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4600,11 +4600,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>15187</v>
+        <v>8933</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4614,39 +4614,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2606000</t>
+          <t>2607545</t>
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46163</v>
+        <v>46205</v>
       </c>
       <c r="G44" t="n">
-        <v>3420</v>
+        <v>812</v>
       </c>
       <c r="H44" t="n">
-        <v>17361.29</v>
+        <v>4769.4</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>3420</v>
+        <v>812</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46167.52511574074</v>
+        <v>46219.4502662037</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>46170</v>
+        <v>46229</v>
       </c>
       <c r="M44" t="n">
-        <v>354.31</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -4658,21 +4658,21 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>17361.29</t>
+          <t>1296/26</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>46190</v>
+        <v>46237</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4695,11 +4695,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7657</v>
+        <v>3550</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4709,65 +4709,65 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2606112</t>
+          <t>2607651</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46165</v>
+        <v>46208</v>
       </c>
       <c r="G45" t="n">
-        <v>2734</v>
+        <v>8524</v>
       </c>
       <c r="H45" t="n">
-        <v>20769.3</v>
+        <v>52818.8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>2734</v>
+        <v>8524</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46188.69032407407</v>
+        <v>46208.38284722222</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46196</v>
+        <v>46218</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>9406.4</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1180/26</t>
+          <t>52818.82</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>46217</v>
+        <v>46229</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4790,11 +4790,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>32474</v>
+        <v>5257</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4804,65 +4804,65 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2606111</t>
+          <t>2607687</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46165</v>
+        <v>46209</v>
       </c>
       <c r="G46" t="n">
-        <v>1282</v>
+        <v>7980</v>
       </c>
       <c r="H46" t="n">
-        <v>4847.14</v>
+        <v>35504.62</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1282</v>
+        <v>7980</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46196.4912962963</v>
+        <v>46210</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>46204</v>
+        <v>46219</v>
       </c>
       <c r="M46" t="n">
-        <v>5651.36</v>
+        <v>724.58</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1174/26</t>
+          <t>71178.31</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>29717</v>
+        <v>11329</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4899,22 +4899,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2606445</t>
+          <t>2607865</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46183</v>
+        <v>46215</v>
       </c>
       <c r="G47" t="n">
-        <v>1738</v>
+        <v>8018</v>
       </c>
       <c r="H47" t="n">
-        <v>12252.9</v>
+        <v>35673.69</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4922,16 +4922,16 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1738</v>
+        <v>8018</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46183.3549537037</v>
+        <v>46215.36673611111</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>46193</v>
+        <v>46224</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>728.03</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4953,11 +4953,11 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>19436.85</t>
+          <t>71178.31</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>46198</v>
+        <v>46238</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>41054</v>
+        <v>4249</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2606444</t>
+          <t>2608096</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46183</v>
+        <v>46221</v>
       </c>
       <c r="G48" t="n">
-        <v>1019</v>
+        <v>6585</v>
       </c>
       <c r="H48" t="n">
-        <v>7183.95</v>
+        <v>31923.55</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5017,28 +5017,28 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1019</v>
+        <v>6585</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46183.3549537037</v>
+        <v>46252.40251157407</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>46194</v>
+        <v>46275</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>19566.05</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>19436.85</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>46198</v>
+        <v>46271</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23261</v>
+        <v>2642</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5089,22 +5089,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ONLY RETAIL PRIVATE LIMITED.</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2606588</t>
+          <t>2608097</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46187</v>
+        <v>46221</v>
       </c>
       <c r="G49" t="n">
-        <v>1476</v>
+        <v>4788</v>
       </c>
       <c r="H49" t="n">
-        <v>10346.76</v>
+        <v>21523.18</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5112,28 +5112,28 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>1476</v>
+        <v>4788</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46210.38983796296</v>
+        <v>46258.46469907407</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>46217</v>
+        <v>46262</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>13191.62</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -5143,11 +5143,11 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10346.76</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>46231</v>
+        <v>46271</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5170,11 +5170,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>38100</v>
+        <v>34930</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5184,65 +5184,65 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2606661</t>
+          <t>2608253</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46188</v>
+        <v>46222</v>
       </c>
       <c r="G50" t="n">
-        <v>509</v>
+        <v>8241</v>
       </c>
       <c r="H50" t="n">
-        <v>2670.16</v>
+        <v>58956.11</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>509</v>
+        <v>8241</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46196.4912962963</v>
+        <v>46222.40752314815</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>46205</v>
+        <v>46232</v>
       </c>
       <c r="M50" t="n">
-        <v>1427.34</v>
+        <v>1203.19</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1174/26</t>
+          <t>58956.11</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>46212</v>
+        <v>46245</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5265,11 +5265,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>43271</v>
+        <v>1350</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5279,65 +5279,65 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2606660</t>
+          <t>2608524</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46188</v>
+        <v>46229</v>
       </c>
       <c r="G51" t="n">
-        <v>2408</v>
+        <v>4973</v>
       </c>
       <c r="H51" t="n">
-        <v>15185.99</v>
+        <v>31329.9</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>2408</v>
+        <v>4973</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46196.49310185185</v>
+        <v>46229.45681712963</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>46199</v>
+        <v>46238</v>
       </c>
       <c r="M51" t="n">
-        <v>4230.01</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1174/26</t>
+          <t>40,868.10</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>46212</v>
+        <v>46245</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5360,11 +5360,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>42697</v>
+        <v>39707</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5374,65 +5374,65 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2606676</t>
+          <t>2608641</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46190</v>
+        <v>46229</v>
       </c>
       <c r="G52" t="n">
-        <v>2390</v>
+        <v>2000</v>
       </c>
       <c r="H52" t="n">
-        <v>27531.01</v>
+        <v>13400</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>2390</v>
+        <v>2000</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46216.59604166666</v>
+        <v>46246.47179398148</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>46221</v>
+        <v>46263</v>
       </c>
       <c r="M52" t="n">
-        <v>3121.19</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1216/26</t>
+          <t>73197.90</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>46225</v>
+        <v>46274</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5455,11 +5455,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>8627</v>
+        <v>4521</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5469,65 +5469,65 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2606677</t>
+          <t>2608642</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46190</v>
+        <v>46229</v>
       </c>
       <c r="G53" t="n">
-        <v>1428</v>
+        <v>1240</v>
       </c>
       <c r="H53" t="n">
-        <v>14550.86</v>
+        <v>8308</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1428</v>
+        <v>1240</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46216.59912037037</v>
+        <v>46246.47179398148</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>46218</v>
+        <v>46263</v>
       </c>
       <c r="M53" t="n">
-        <v>2688.64</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1216/26</t>
+          <t>73197.90</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>46225</v>
+        <v>46274</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5550,11 +5550,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>42888</v>
+        <v>2361</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5564,65 +5564,65 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2607032</t>
+          <t>2608649</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46195</v>
+        <v>46230</v>
       </c>
       <c r="G54" t="n">
-        <v>1240</v>
+        <v>274</v>
       </c>
       <c r="H54" t="n">
-        <v>13963.79</v>
+        <v>1726.2</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>1240</v>
+        <v>274</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46197.74751157407</v>
+        <v>46230.43035879629</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>46201</v>
+        <v>46238</v>
       </c>
       <c r="M54" t="n">
-        <v>1474.21</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1180/26</t>
+          <t>40,868.10</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>46217</v>
+        <v>46245</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5645,11 +5645,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>22486</v>
+        <v>42544</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5659,65 +5659,65 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2607031</t>
+          <t>2608650</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46195</v>
+        <v>46230</v>
       </c>
       <c r="G55" t="n">
-        <v>630</v>
+        <v>1240</v>
       </c>
       <c r="H55" t="n">
-        <v>6661.87</v>
+        <v>7812</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>630</v>
+        <v>1240</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46197.73806712963</v>
+        <v>46230.43035879629</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="M55" t="n">
-        <v>1181.63</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1174/26</t>
+          <t>40,868.10</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>46212</v>
+        <v>46245</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5740,11 +5740,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>12095</v>
+        <v>8172</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5754,36 +5754,36 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2607069</t>
+          <t>2608677</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46197</v>
+        <v>46231</v>
       </c>
       <c r="G56" t="n">
-        <v>2365</v>
+        <v>405</v>
       </c>
       <c r="H56" t="n">
-        <v>13953.5</v>
+        <v>2389.5</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>2301</v>
+        <v>405</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46197.37570601852</v>
+        <v>46236.65753472222</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>46201</v>
+        <v>46250</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -5798,21 +5798,21 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>27529.40</t>
+          <t>1390/26</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>46212</v>
+        <v>46261</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5835,11 +5835,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>39643</v>
+        <v>31953</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5849,36 +5849,36 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2607070</t>
+          <t>2608678</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46197</v>
+        <v>46231</v>
       </c>
       <c r="G57" t="n">
-        <v>2301</v>
+        <v>262</v>
       </c>
       <c r="H57" t="n">
-        <v>13575.9</v>
+        <v>1545.8</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2365</v>
+        <v>262</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46197.37570601852</v>
+        <v>46237.66037037037</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>46201</v>
+        <v>46240</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -5888,26 +5888,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>27529.40</t>
+          <t>1390/26</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>46212</v>
+        <v>46261</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5930,11 +5930,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>28351</v>
+        <v>20166</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5944,39 +5944,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2607407</t>
+          <t>2609047</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46201</v>
+        <v>46243</v>
       </c>
       <c r="G58" t="n">
-        <v>8784</v>
+        <v>10106</v>
       </c>
       <c r="H58" t="n">
-        <v>46484.93</v>
+        <v>66742.45</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>8784</v>
+        <v>10106</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46201.3633449074</v>
+        <v>46243.43114583333</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>46209</v>
+        <v>46250</v>
       </c>
       <c r="M58" t="n">
-        <v>948.67</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -5988,21 +5988,21 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>46484.93</t>
+          <t>1390/26</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>46216</v>
+        <v>46261</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6025,11 +6025,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>44410</v>
+        <v>6361</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6039,36 +6039,36 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2607449</t>
+          <t>2609048</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46204</v>
+        <v>46243</v>
       </c>
       <c r="G59" t="n">
-        <v>1880</v>
+        <v>418</v>
       </c>
       <c r="H59" t="n">
-        <v>11844</v>
+        <v>2766.2</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1880</v>
+        <v>418</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46205.38795138889</v>
+        <v>46243.42872685185</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>46216</v>
+        <v>46253</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6083,21 +6083,21 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>21370.50</t>
+          <t>1390/26</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>46222</v>
+        <v>46261</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4232</v>
+        <v>22108</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6134,22 +6134,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2607448</t>
+          <t>2609112</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46204</v>
+        <v>46243</v>
       </c>
       <c r="G60" t="n">
-        <v>1450</v>
+        <v>5852</v>
       </c>
       <c r="H60" t="n">
-        <v>9526.5</v>
+        <v>26036.72</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6157,16 +6157,16 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1450</v>
+        <v>5852</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46205.38795138889</v>
+        <v>46243.42559027778</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>46216</v>
+        <v>46253</v>
       </c>
       <c r="M60" t="n">
-        <v>1058.5</v>
+        <v>531.36</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -6188,11 +6188,11 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>21370.50</t>
+          <t>84872.08</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>46222</v>
+        <v>46268</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6215,11 +6215,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>41998</v>
+        <v>25768</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6229,65 +6229,65 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2607545</t>
+          <t>2609270</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46205</v>
+        <v>46247</v>
       </c>
       <c r="G61" t="n">
-        <v>812</v>
+        <v>1882</v>
       </c>
       <c r="H61" t="n">
-        <v>4769.4</v>
+        <v>8124.6</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>812</v>
+        <v>1882</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46219.4502662037</v>
+        <v>46247.51739583333</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>46229</v>
+        <v>46252</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>5416.4</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1296/26</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>46237</v>
+        <v>46271</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6310,11 +6310,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>15337</v>
+        <v>15585</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6324,65 +6324,65 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2607546</t>
+          <t>2609284</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46205</v>
+        <v>46250</v>
       </c>
       <c r="G62" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="H62" t="n">
-        <v>2350</v>
+        <v>14308</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46219.46043981481</v>
+        <v>46250.38284722222</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>46223</v>
+        <v>46264</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1296/26</t>
+          <t>84872.08</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>46237</v>
+        <v>46268</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>24227</v>
+        <v>13030</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6419,22 +6419,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2607651</t>
+          <t>2609283</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46208</v>
+        <v>46250</v>
       </c>
       <c r="G63" t="n">
-        <v>8524</v>
+        <v>6612</v>
       </c>
       <c r="H63" t="n">
-        <v>52818.8</v>
+        <v>29418.11</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6442,16 +6442,16 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>8524</v>
+        <v>6612</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46208.38284722222</v>
+        <v>46250.38120370371</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>46218</v>
+        <v>46264</v>
       </c>
       <c r="M63" t="n">
-        <v>9406.4</v>
+        <v>600.37</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6473,11 +6473,11 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>52818.82</t>
+          <t>84872.08</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>46229</v>
+        <v>46268</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>37861</v>
+        <v>36958</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6519,17 +6519,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2607687</t>
+          <t>2609285</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46209</v>
+        <v>46250</v>
       </c>
       <c r="G64" t="n">
-        <v>7980</v>
+        <v>2112</v>
       </c>
       <c r="H64" t="n">
-        <v>35504.62</v>
+        <v>15109.25</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6537,16 +6537,16 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>7980</v>
+        <v>2112</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46210</v>
+        <v>46250.38284722222</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>46219</v>
+        <v>46264</v>
       </c>
       <c r="M64" t="n">
-        <v>724.58</v>
+        <v>308.35</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -6568,11 +6568,11 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>71178.31</t>
+          <t>84872.08</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46238</v>
+        <v>46268</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>5971</v>
+        <v>1733</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2607865</t>
+          <t>2609418</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46215</v>
+        <v>46251</v>
       </c>
       <c r="G65" t="n">
-        <v>8018</v>
+        <v>1200</v>
       </c>
       <c r="H65" t="n">
-        <v>35673.69</v>
+        <v>9240</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -6632,16 +6632,16 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>8018</v>
+        <v>1200</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46215.36673611111</v>
+        <v>46259.45524305556</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>46224</v>
+        <v>46265</v>
       </c>
       <c r="M65" t="n">
-        <v>728.03</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6663,11 +6663,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>71178.31</t>
+          <t>73197.90</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46238</v>
+        <v>46274</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>17923</v>
+        <v>585</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6704,22 +6704,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2608253</t>
+          <t>2609419</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46222</v>
+        <v>46251</v>
       </c>
       <c r="G66" t="n">
-        <v>8241</v>
+        <v>5487</v>
       </c>
       <c r="H66" t="n">
-        <v>58956.11</v>
+        <v>42249.9</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -6727,16 +6727,16 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>8241</v>
+        <v>5487</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46222.40752314815</v>
+        <v>46259.45524305556</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="M66" t="n">
-        <v>1203.19</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6758,11 +6758,11 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>58956.11</t>
+          <t>73197.90</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>46245</v>
+        <v>46274</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>19120</v>
+        <v>22485</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -6799,22 +6799,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2608524</t>
+          <t>2609438</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46229</v>
+        <v>46252</v>
       </c>
       <c r="G67" t="n">
-        <v>4973</v>
+        <v>8334</v>
       </c>
       <c r="H67" t="n">
-        <v>31329.9</v>
+        <v>33705.8</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -6822,28 +6822,28 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>4973</v>
+        <v>8334</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46229.45681712963</v>
+        <v>46252.40453703704</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>46238</v>
+        <v>46256</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>20658.4</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6853,11 +6853,11 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>40,868.10</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>46245</v>
+        <v>46271</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>29178</v>
+        <v>18477</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -6894,22 +6894,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2608649</t>
+          <t>2609878</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46230</v>
+        <v>46264</v>
       </c>
       <c r="G68" t="n">
-        <v>274</v>
+        <v>900</v>
       </c>
       <c r="H68" t="n">
-        <v>1726.2</v>
+        <v>6300</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>274</v>
+        <v>900</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46230.43035879629</v>
+        <v>46274.64322916666</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>46238</v>
+        <v>46283</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -6948,11 +6948,11 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>40,868.10</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>46245</v>
+        <v>46288</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18900</v>
+        <v>37371</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -6989,22 +6989,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2608650</t>
+          <t>2609877</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46230</v>
+        <v>46264</v>
       </c>
       <c r="G69" t="n">
-        <v>1240</v>
+        <v>2368</v>
       </c>
       <c r="H69" t="n">
-        <v>7812</v>
+        <v>16576</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1240</v>
+        <v>2368</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46230.43035879629</v>
+        <v>46274.64322916666</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>46238</v>
+        <v>46283</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7043,11 +7043,11 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>40,868.10</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>46245</v>
+        <v>46288</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7070,11 +7070,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>50337</v>
+        <v>7738</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7084,36 +7084,36 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2608677</t>
+          <t>2609879</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46231</v>
+        <v>46264</v>
       </c>
       <c r="G70" t="n">
-        <v>405</v>
+        <v>15717</v>
       </c>
       <c r="H70" t="n">
-        <v>2389.5</v>
+        <v>110019</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>405</v>
+        <v>15717</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46236.65753472222</v>
+        <v>46274.64322916666</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>46250</v>
+        <v>46283</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7128,21 +7128,21 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1390/26</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>46261</v>
+        <v>46288</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7165,11 +7165,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>44477</v>
+        <v>21027</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7179,65 +7179,65 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2608678</t>
+          <t>2610178</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46231</v>
+        <v>46271</v>
       </c>
       <c r="G71" t="n">
-        <v>262</v>
+        <v>10982</v>
       </c>
       <c r="H71" t="n">
-        <v>1545.8</v>
+        <v>48861.11</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>262</v>
+        <v>10982</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46237.66037037037</v>
+        <v>46271.53631944444</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>46240</v>
+        <v>46285</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>997.17</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1390/26</t>
+          <t>52958.59</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>46261</v>
+        <v>46287</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>35050</v>
+        <v>41520</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -7279,17 +7279,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2609048</t>
+          <t>2610184</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46243</v>
+        <v>46273</v>
       </c>
       <c r="G72" t="n">
-        <v>418</v>
+        <v>1635</v>
       </c>
       <c r="H72" t="n">
-        <v>2766.2</v>
+        <v>7708.95</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -7297,16 +7297,16 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>418</v>
+        <v>1635</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46243.42872685185</v>
+        <v>46272.45939814814</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>46253</v>
+        <v>46284</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1492.4</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -7328,11 +7328,11 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1390/26</t>
+          <t>43695.75</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>46261</v>
+        <v>46289</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3890</v>
+        <v>22215</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -7374,17 +7374,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2609047</t>
+          <t>2610183</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46243</v>
+        <v>46273</v>
       </c>
       <c r="G73" t="n">
-        <v>10106</v>
+        <v>5167</v>
       </c>
       <c r="H73" t="n">
-        <v>66742.45</v>
+        <v>23295.9</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -7392,16 +7392,16 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>10106</v>
+        <v>5167</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46243.43114583333</v>
+        <v>46272.46409722222</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>46250</v>
+        <v>46282</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>7430.4</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -7423,11 +7423,11 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1390/26</t>
+          <t>43695.75</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>46261</v>
+        <v>46289</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7450,11 +7450,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>17483</v>
+        <v>20721</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7464,39 +7464,39 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2609112</t>
+          <t>2610275</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46243</v>
+        <v>46275</v>
       </c>
       <c r="G74" t="n">
-        <v>5852</v>
+        <v>1052</v>
       </c>
       <c r="H74" t="n">
-        <v>26036.72</v>
+        <v>9792.1</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>5852</v>
+        <v>1052</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46243.42559027778</v>
+        <v>46275.37585648148</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>46253</v>
+        <v>46282</v>
       </c>
       <c r="M74" t="n">
-        <v>531.36</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -7508,21 +7508,21 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>84872.08</t>
+          <t>43695.75</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>46268</v>
+        <v>46289</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7545,11 +7545,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>33138</v>
+        <v>15300</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7559,39 +7559,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2609284</t>
+          <t>2610276</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46250</v>
+        <v>46275</v>
       </c>
       <c r="G75" t="n">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="H75" t="n">
-        <v>14308</v>
+        <v>2898.8</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46250.38284722222</v>
+        <v>46275.37873842593</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>46264</v>
+        <v>46284</v>
       </c>
       <c r="M75" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -7603,21 +7603,21 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>84872.08</t>
+          <t>43695.75</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>46268</v>
+        <v>46289</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7633,196 +7633,6 @@
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>8303</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MGKFL</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Sweater</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Matalan</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2609283</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="G76" t="n">
-        <v>6612</v>
-      </c>
-      <c r="H76" t="n">
-        <v>29418.11</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>MGKFL</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>6612</v>
-      </c>
-      <c r="K76" s="1" t="n">
-        <v>46250.38120370371</v>
-      </c>
-      <c r="L76" s="1" t="n">
-        <v>46264</v>
-      </c>
-      <c r="M76" t="n">
-        <v>600.37</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Sea</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>DBBL</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>84872.08</t>
-        </is>
-      </c>
-      <c r="S76" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Realize Pending</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>32943</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MGKFL</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Sweater</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Matalan</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2609285</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2112</v>
-      </c>
-      <c r="H77" t="n">
-        <v>15109.25</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>MGKFL</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>2112</v>
-      </c>
-      <c r="K77" s="1" t="n">
-        <v>46250.38284722222</v>
-      </c>
-      <c r="L77" s="1" t="n">
-        <v>46264</v>
-      </c>
-      <c r="M77" t="n">
-        <v>308.35</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Sea</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>DBBL</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>84872.08</t>
-        </is>
-      </c>
-      <c r="S77" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Realize Pending</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/OUTPUT/RealizeReports/Nowshin.xlsx
+++ b/OUTPUT/RealizeReports/Nowshin.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Nowshin" displayName="Nowshin" ref="A1:Y75" headerRowCount="1">
-  <autoFilter ref="A1:Y75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Nowshin" displayName="Nowshin" ref="A1:Y82" headerRowCount="1">
+  <autoFilter ref="A1:Y82"/>
   <tableColumns count="25">
     <tableColumn id="1" name="SL"/>
     <tableColumn id="2" name="LC_Factory"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y75"/>
+  <dimension ref="A1:Y82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,11 +610,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>41449</v>
+        <v>22788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -624,22 +624,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Auric Sourcing BD</t>
+          <t>Hellenic Trading AB</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2411147</t>
+          <t>2315555</t>
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45500</v>
+        <v>45232</v>
       </c>
       <c r="G2" t="n">
-        <v>1033</v>
+        <v>14380</v>
       </c>
       <c r="H2" t="n">
-        <v>4583.65</v>
+        <v>32421.58</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1033</v>
+        <v>14380</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>45516.35745370371</v>
+        <v>45290.36759259259</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>45537</v>
+        <v>45302</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>652.42</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -668,21 +668,21 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>ABL</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>FDC-2689</t>
+          <t>FDBC-82/24</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>45519</v>
+        <v>45308</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -705,11 +705,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15566</v>
+        <v>18746</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Auric Sourcing BD</t>
+          <t>Hellenic Trading AB</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2411200</t>
+          <t>2316015</t>
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45501</v>
+        <v>45244</v>
       </c>
       <c r="G3" t="n">
-        <v>152</v>
+        <v>21284</v>
       </c>
       <c r="H3" t="n">
-        <v>676.4</v>
+        <v>69531.05</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -742,16 +742,16 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>152</v>
+        <v>21284</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>45516.35745370371</v>
+        <v>45288.41481481482</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>45519</v>
+        <v>45302</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>9219.75</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -763,21 +763,21 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KAZAKHSTAN</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>ABL</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>FDC2688</t>
+          <t>083-24</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>45519</v>
+        <v>45308</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -800,11 +800,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10315</v>
+        <v>28427</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -814,65 +814,65 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>Hellenic Trading AB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2411802</t>
+          <t>2317394</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45512</v>
+        <v>45265</v>
       </c>
       <c r="G4" t="n">
-        <v>2107</v>
+        <v>21596</v>
       </c>
       <c r="H4" t="n">
-        <v>12027.6</v>
+        <v>50902.57</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2007</v>
+        <v>21596</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>45512.77430555555</v>
+        <v>45311.37347222222</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>45528</v>
+        <v>45319</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>6326.83</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sea/Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>3318/24</t>
+          <t>FDBC-0456/24</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>45558</v>
+        <v>45334</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13181</v>
+        <v>19327</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -909,51 +909,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>Auric Sourcing BD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2411945</t>
+          <t>2411147</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45515</v>
+        <v>45500</v>
       </c>
       <c r="G5" t="n">
-        <v>5511</v>
+        <v>1033</v>
       </c>
       <c r="H5" t="n">
-        <v>35862.83</v>
+        <v>4583.65</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5511</v>
+        <v>1033</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>45522.37118055556</v>
+        <v>45516.35745370371</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>45536</v>
+        <v>45537</v>
       </c>
       <c r="M5" t="n">
-        <v>1887.52</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sea/Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -963,11 +963,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3166/24</t>
+          <t>FDC-2689</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>45552</v>
+        <v>45519</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>28424</v>
+        <v>42702</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1004,39 +1004,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>Auric Sourcing BD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2412017</t>
+          <t>2411200</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45518</v>
+        <v>45501</v>
       </c>
       <c r="G6" t="n">
-        <v>20248</v>
+        <v>152</v>
       </c>
       <c r="H6" t="n">
-        <v>131599.32</v>
+        <v>676.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>20248</v>
+        <v>152</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>45518.76497685185</v>
+        <v>45516.35745370371</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>45527</v>
+        <v>45519</v>
       </c>
       <c r="M6" t="n">
-        <v>6926.28</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>KAZAKHSTAN</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1058,11 +1058,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3166/24</t>
+          <t>FDC2688</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>45552</v>
+        <v>45519</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>31476</v>
+        <v>33421</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Best Seller</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2412270</t>
+          <t>2411802</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>45524</v>
+        <v>45512</v>
       </c>
       <c r="G7" t="n">
-        <v>4718</v>
+        <v>2107</v>
       </c>
       <c r="H7" t="n">
-        <v>29492.22</v>
+        <v>12027.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1122,28 +1122,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4718</v>
+        <v>2007</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>45545.45666666667</v>
+        <v>45512.77430555555</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>45547</v>
+        <v>45528</v>
       </c>
       <c r="M7" t="n">
-        <v>1552.22</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea/Air</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1153,11 +1153,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3319/24</t>
+          <t>3318/24</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>45561</v>
+        <v>45558</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>42001</v>
+        <v>17588</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2412586</t>
+          <t>2411945</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>45533</v>
+        <v>45515</v>
       </c>
       <c r="G8" t="n">
-        <v>570</v>
+        <v>5511</v>
       </c>
       <c r="H8" t="n">
-        <v>3221.92</v>
+        <v>35862.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1217,23 +1217,23 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>570</v>
+        <v>5511</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>45532.47994212963</v>
+        <v>45522.37118055556</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>45542</v>
+        <v>45536</v>
       </c>
       <c r="M8" t="n">
-        <v>169.58</v>
+        <v>1887.52</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Sea/Air</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3319/24</t>
+          <t>3166/24</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>45561</v>
+        <v>45552</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>30890</v>
+        <v>10385</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2412745</t>
+          <t>2412017</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45535</v>
+        <v>45518</v>
       </c>
       <c r="G9" t="n">
-        <v>6680</v>
+        <v>20248</v>
       </c>
       <c r="H9" t="n">
-        <v>43470.1</v>
+        <v>131599.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6680</v>
+        <v>20248</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>45533.53450231482</v>
+        <v>45518.76497685185</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>45542</v>
+        <v>45527</v>
       </c>
       <c r="M9" t="n">
-        <v>2287.9</v>
+        <v>6926.28</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>3319/24</t>
+          <t>3166/24</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>45561</v>
+        <v>45552</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1370,11 +1370,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27298</v>
+        <v>3757</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1384,65 +1384,65 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TMS Fashion (HK) Ltd.</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2412874</t>
+          <t>2412270</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45536</v>
+        <v>45524</v>
       </c>
       <c r="G10" t="n">
-        <v>851</v>
+        <v>4718</v>
       </c>
       <c r="H10" t="n">
-        <v>6808</v>
+        <v>29492.22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>851</v>
+        <v>4718</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>45540.7222800926</v>
+        <v>45545.45666666667</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>45549</v>
+        <v>45547</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1552.22</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2261/24</t>
+          <t>3319/24</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>45559</v>
+        <v>45561</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>28776</v>
+        <v>1549</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1479,39 +1479,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BSI APPAREL LTD</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2412924</t>
+          <t>2412586</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>45539</v>
+        <v>45533</v>
       </c>
       <c r="G11" t="n">
-        <v>10489</v>
+        <v>570</v>
       </c>
       <c r="H11" t="n">
-        <v>69809.89</v>
+        <v>3221.92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10489</v>
+        <v>570</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>45540.71069444445</v>
+        <v>45532.47994212963</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>45550</v>
+        <v>45542</v>
       </c>
       <c r="M11" t="n">
-        <v>2999.76</v>
+        <v>169.58</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>69809.65</t>
+          <t>3319/24</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1560,11 +1560,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>28894</v>
+        <v>40780</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1574,39 +1574,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2413872</t>
+          <t>2412745</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>45556</v>
+        <v>45535</v>
       </c>
       <c r="G12" t="n">
-        <v>21180</v>
+        <v>6680</v>
       </c>
       <c r="H12" t="n">
-        <v>41168.66</v>
+        <v>43470.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>21180</v>
+        <v>6680</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>45592.36891203704</v>
+        <v>45533.53450231482</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>45606</v>
+        <v>45542</v>
       </c>
       <c r="M12" t="n">
-        <v>3309.34</v>
+        <v>2287.9</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>$122722.40</t>
+          <t>3319/24</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>45641</v>
+        <v>45561</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>42494</v>
+        <v>24</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1669,22 +1669,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hellenic</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2413871</t>
+          <t>2412874</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>45556</v>
+        <v>45536</v>
       </c>
       <c r="G13" t="n">
-        <v>20880</v>
+        <v>851</v>
       </c>
       <c r="H13" t="n">
-        <v>44561.32</v>
+        <v>6808</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>20880</v>
+        <v>851</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>45591.42358796296</v>
+        <v>45540.7222800926</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>45597</v>
+        <v>45549</v>
       </c>
       <c r="M13" t="n">
-        <v>3462.68</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>$122722.40</t>
+          <t>2261/24</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>45641</v>
+        <v>45559</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17107</v>
+        <v>19943</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1764,22 +1764,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AAMARA TEX LTD</t>
+          <t>BSI APPAREL LTD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2414546</t>
+          <t>2412924</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>45568</v>
+        <v>45539</v>
       </c>
       <c r="G14" t="n">
-        <v>4134</v>
+        <v>10489</v>
       </c>
       <c r="H14" t="n">
-        <v>24846</v>
+        <v>69809.89</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1787,16 +1787,16 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4134</v>
+        <v>10489</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>45568.66247685185</v>
+        <v>45540.71069444445</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>45576</v>
+        <v>45550</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2999.76</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1818,11 +1818,11 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>54,184.80</t>
+          <t>69809.65</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>45624</v>
+        <v>45561</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1845,11 +1845,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2946</v>
+        <v>15806</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1859,22 +1859,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AAMARA TEX LTD</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2414532</t>
+          <t>2413872</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>45568</v>
+        <v>45556</v>
       </c>
       <c r="G15" t="n">
-        <v>4896</v>
+        <v>21180</v>
       </c>
       <c r="H15" t="n">
-        <v>29338.8</v>
+        <v>41168.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1882,16 +1882,16 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4896</v>
+        <v>21180</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>45568.65729166667</v>
+        <v>45592.36891203704</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>45576</v>
+        <v>45606</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3309.34</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Felixtowe</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>54,184.80</t>
+          <t>$122722.40</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>45624</v>
+        <v>45641</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>339</v>
+        <v>31012</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1959,17 +1959,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2414982</t>
+          <t>2413871</t>
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>45577</v>
+        <v>45556</v>
       </c>
       <c r="G16" t="n">
-        <v>30168</v>
+        <v>20880</v>
       </c>
       <c r="H16" t="n">
-        <v>115847.9</v>
+        <v>44561.32</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1977,16 +1977,16 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>30168</v>
+        <v>20880</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>45614.55766203703</v>
+        <v>45591.42358796296</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>45617</v>
+        <v>45597</v>
       </c>
       <c r="M16" t="n">
-        <v>1807.3</v>
+        <v>3462.68</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2008,11 +2008,11 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>$115847.87</t>
+          <t>$122722.40</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>45643</v>
+        <v>45641</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2035,50 +2035,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4261</v>
+        <v>12510</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AAMARA TEX LTD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2414532</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4896</v>
+      </c>
+      <c r="H17" t="n">
+        <v>29338.8</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>MFSL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sweater</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Hellenic</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2415532</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>45589</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4218</v>
-      </c>
-      <c r="H17" t="n">
-        <v>18348.3</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MGKFL</t>
-        </is>
-      </c>
       <c r="J17" t="n">
-        <v>4218</v>
+        <v>4896</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>45588.67109953704</v>
+        <v>45568.65729166667</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>45584</v>
+        <v>45576</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2088,26 +2088,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Felixtowe</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>$18348.30</t>
+          <t>54,184.80</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>45609</v>
+        <v>45624</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2130,50 +2130,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14296</v>
+        <v>1220</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AAMARA TEX LTD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2414546</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4134</v>
+      </c>
+      <c r="H18" t="n">
+        <v>24846</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>MFSL</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Sweater</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Hellenic</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2415704</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>45591</v>
-      </c>
-      <c r="G18" t="n">
-        <v>6174</v>
-      </c>
-      <c r="H18" t="n">
-        <v>26856.9</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>MGKFL</t>
-        </is>
-      </c>
       <c r="J18" t="n">
-        <v>6174</v>
+        <v>4134</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>45592.48755787037</v>
+        <v>45568.66247685185</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>45597</v>
+        <v>45576</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2183,26 +2183,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>54,184.80</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>45739</v>
+        <v>45624</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>27251</v>
+        <v>22768</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2244,17 +2244,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2415858</t>
+          <t>2414982</t>
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45594</v>
+        <v>45577</v>
       </c>
       <c r="G19" t="n">
-        <v>17560</v>
+        <v>30168</v>
       </c>
       <c r="H19" t="n">
-        <v>36992.46</v>
+        <v>115847.9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2262,16 +2262,16 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17560</v>
+        <v>30168</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>45593.44770833333</v>
+        <v>45614.55766203703</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>45608</v>
+        <v>45617</v>
       </c>
       <c r="M19" t="n">
-        <v>3395.54</v>
+        <v>1807.3</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2293,11 +2293,11 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>$122722.40</t>
+          <t>$115847.87</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>45641</v>
+        <v>45643</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>26125</v>
+        <v>15219</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2339,17 +2339,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2416908</t>
+          <t>2415532</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>45615</v>
+        <v>45589</v>
       </c>
       <c r="G20" t="n">
-        <v>2002</v>
+        <v>4218</v>
       </c>
       <c r="H20" t="n">
-        <v>8708.700000000001</v>
+        <v>18348.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2002</v>
+        <v>4218</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>45617.68335648148</v>
+        <v>45588.67109953704</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>45617</v>
+        <v>45584</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>$18348.30</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>45739</v>
+        <v>45609</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13700</v>
+        <v>7778</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2434,17 +2434,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2416909</t>
+          <t>2415704</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>45615</v>
+        <v>45591</v>
       </c>
       <c r="G21" t="n">
-        <v>2002</v>
+        <v>6174</v>
       </c>
       <c r="H21" t="n">
-        <v>8708.700000000001</v>
+        <v>26856.9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2002</v>
+        <v>6174</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>45617.67180555555</v>
+        <v>45592.48755787037</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>45617</v>
+        <v>45597</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2510,7 +2510,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14624</v>
+        <v>35627</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2529,46 +2529,46 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2416910</t>
+          <t>2415858</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>45615</v>
+        <v>45594</v>
       </c>
       <c r="G22" t="n">
-        <v>2002</v>
+        <v>17560</v>
       </c>
       <c r="H22" t="n">
-        <v>8708.700000000001</v>
+        <v>36992.46</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2002</v>
+        <v>17560</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>45617.67793981481</v>
+        <v>45593.44770833333</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>45617</v>
+        <v>45608</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3395.54</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2578,11 +2578,11 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0745/2025</t>
+          <t>$122722.40</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>45739</v>
+        <v>45641</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2509</v>
+        <v>12503</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2416907</t>
+          <t>2416911</t>
         </is>
       </c>
       <c r="F23" s="1" t="n">
@@ -2645,7 +2645,7 @@
         <v>2002</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>45617.67793981481</v>
+        <v>45617.67180555555</v>
       </c>
       <c r="L23" s="1" t="n">
         <v>45617</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>18190</v>
+        <v>28195</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10849</v>
+        <v>16561</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2416911</t>
+          <t>2416907</t>
         </is>
       </c>
       <c r="F25" s="1" t="n">
@@ -2835,7 +2835,7 @@
         <v>2002</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>45617.67180555555</v>
+        <v>45617.67793981481</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>45617</v>
@@ -2890,11 +2890,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22603</v>
+        <v>9263</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2904,22 +2904,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Michael Kors (USA), Inc.</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2604775</t>
+          <t>2416910</t>
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>46141</v>
+        <v>45615</v>
       </c>
       <c r="G26" t="n">
-        <v>24240</v>
+        <v>2002</v>
       </c>
       <c r="H26" t="n">
-        <v>150772.8</v>
+        <v>8708.700000000001</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>24240</v>
+        <v>2002</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46160.52238425926</v>
+        <v>45617.67793981481</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>46167</v>
+        <v>45617</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2943,26 +2943,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2052/2026</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>46177</v>
+        <v>45739</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2985,11 +2985,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>19205</v>
+        <v>33755</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2999,22 +2999,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2605751</t>
+          <t>2416908</t>
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>46160</v>
+        <v>45615</v>
       </c>
       <c r="G27" t="n">
-        <v>693</v>
+        <v>2002</v>
       </c>
       <c r="H27" t="n">
-        <v>4097.48</v>
+        <v>8708.700000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3022,42 +3022,42 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>693</v>
+        <v>2002</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46271.53631944444</v>
+        <v>45617.68335648148</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46284</v>
+        <v>45617</v>
       </c>
       <c r="M27" t="n">
-        <v>83.62</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jabel-Ali</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>52958.59</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>46287</v>
+        <v>45739</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3080,11 +3080,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>24425</v>
+        <v>30781</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>Hellenic</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2605750</t>
+          <t>2416909</t>
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>46160</v>
+        <v>45615</v>
       </c>
       <c r="G28" t="n">
-        <v>14010</v>
+        <v>2002</v>
       </c>
       <c r="H28" t="n">
-        <v>74650.52</v>
+        <v>8708.700000000001</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3117,42 +3117,42 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>18456</v>
+        <v>2002</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46161</v>
+        <v>45617.67180555555</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>46184</v>
+        <v>45617</v>
       </c>
       <c r="M28" t="n">
-        <v>1523.48</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>98178.75</t>
+          <t>0745/2025</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>46222</v>
+        <v>45739</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3175,11 +3175,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>38158</v>
+        <v>21521</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3189,65 +3189,65 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Michael Kors (USA), Inc.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2606111</t>
+          <t>2604775</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>46165</v>
+        <v>46141</v>
       </c>
       <c r="G29" t="n">
-        <v>1282</v>
+        <v>24240</v>
       </c>
       <c r="H29" t="n">
-        <v>4847.14</v>
+        <v>150772.8</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1282</v>
+        <v>24240</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46196.4912962963</v>
+        <v>46160.52238425926</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>46204</v>
+        <v>46167</v>
       </c>
       <c r="M29" t="n">
-        <v>5651.36</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1174/26</t>
+          <t>2052/2026</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>46212</v>
+        <v>46177</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3270,11 +3270,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>33404</v>
+        <v>3555</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3284,65 +3284,65 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2606112</t>
+          <t>2605751</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>46165</v>
+        <v>46160</v>
       </c>
       <c r="G30" t="n">
-        <v>2734</v>
+        <v>693</v>
       </c>
       <c r="H30" t="n">
-        <v>20769.3</v>
+        <v>4097.48</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>2734</v>
+        <v>693</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46188.69032407407</v>
+        <v>46271.53631944444</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>46196</v>
+        <v>46284</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>83.62</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Jabel-Ali</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1180/26</t>
+          <t>52958.59</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>46217</v>
+        <v>46287</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16439</v>
+        <v>19819</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3379,22 +3379,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ZXY</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2606424</t>
+          <t>2605750</t>
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>46180</v>
+        <v>46160</v>
       </c>
       <c r="G31" t="n">
-        <v>3570</v>
+        <v>14010</v>
       </c>
       <c r="H31" t="n">
-        <v>17562.96</v>
+        <v>74650.52</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3402,28 +3402,28 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>3570</v>
+        <v>18456</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46231.41276620371</v>
+        <v>46161</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>46238</v>
+        <v>46184</v>
       </c>
       <c r="M31" t="n">
-        <v>11708.64</v>
+        <v>1523.48</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3433,11 +3433,11 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3323/2026/2026090200147398</t>
+          <t>98178.75</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>46271</v>
+        <v>46222</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3460,11 +3460,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34076</v>
+        <v>29592</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3474,65 +3474,65 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ONLY RETAIL PRIVATE LIMITED.</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2606588</t>
+          <t>2606111</t>
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>46187</v>
+        <v>46165</v>
       </c>
       <c r="G32" t="n">
-        <v>1476</v>
+        <v>1282</v>
       </c>
       <c r="H32" t="n">
-        <v>10346.76</v>
+        <v>4847.14</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1476</v>
+        <v>1282</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46210.38983796296</v>
+        <v>46196.4912962963</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>46217</v>
+        <v>46204</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>5651.36</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10346.76</t>
+          <t>1174/26</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>46231</v>
+        <v>46212</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>25795</v>
+        <v>37534</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3574,17 +3574,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2606660</t>
+          <t>2606112</t>
         </is>
       </c>
       <c r="F33" s="1" t="n">
-        <v>46188</v>
+        <v>46165</v>
       </c>
       <c r="G33" t="n">
-        <v>2408</v>
+        <v>2734</v>
       </c>
       <c r="H33" t="n">
-        <v>15185.99</v>
+        <v>20769.3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3592,16 +3592,16 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2408</v>
+        <v>2734</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46196.49310185185</v>
+        <v>46188.69032407407</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>46199</v>
+        <v>46196</v>
       </c>
       <c r="M33" t="n">
-        <v>4230.01</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -3623,11 +3623,11 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1174/26</t>
+          <t>1180/26</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>46212</v>
+        <v>46217</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3650,11 +3650,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5308</v>
+        <v>5320</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3664,39 +3664,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2606661</t>
+          <t>2606424</t>
         </is>
       </c>
       <c r="F34" s="1" t="n">
-        <v>46188</v>
+        <v>46180</v>
       </c>
       <c r="G34" t="n">
-        <v>509</v>
+        <v>3570</v>
       </c>
       <c r="H34" t="n">
-        <v>2670.16</v>
+        <v>17562.96</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>509</v>
+        <v>3570</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46196.4912962963</v>
+        <v>46231.41276620371</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>46205</v>
+        <v>46238</v>
       </c>
       <c r="M34" t="n">
-        <v>1427.34</v>
+        <v>11708.64</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3708,21 +3708,21 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1174/26</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>46212</v>
+        <v>46271</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3745,11 +3745,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>40912</v>
+        <v>8686</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3759,65 +3759,65 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>ONLY RETAIL PRIVATE LIMITED.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2606676</t>
+          <t>2606588</t>
         </is>
       </c>
       <c r="F35" s="1" t="n">
-        <v>46190</v>
+        <v>46187</v>
       </c>
       <c r="G35" t="n">
-        <v>2390</v>
+        <v>1476</v>
       </c>
       <c r="H35" t="n">
-        <v>27531.01</v>
+        <v>10346.76</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>2390</v>
+        <v>1476</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46216.59604166666</v>
+        <v>46210.38983796296</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>46221</v>
+        <v>46217</v>
       </c>
       <c r="M35" t="n">
-        <v>3121.19</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>India</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1216/26</t>
+          <t>10346.76</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34101</v>
+        <v>17498</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3859,17 +3859,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2606677</t>
+          <t>2606660</t>
         </is>
       </c>
       <c r="F36" s="1" t="n">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="G36" t="n">
-        <v>1428</v>
+        <v>2408</v>
       </c>
       <c r="H36" t="n">
-        <v>14550.86</v>
+        <v>15185.99</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3877,16 +3877,16 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1428</v>
+        <v>2408</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46216.59912037037</v>
+        <v>46196.49310185185</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>46218</v>
+        <v>46199</v>
       </c>
       <c r="M36" t="n">
-        <v>2688.64</v>
+        <v>4230.01</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1216/26</t>
+          <t>1174/26</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1890</v>
+        <v>6002</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3954,17 +3954,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2607031</t>
+          <t>2606661</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="G37" t="n">
-        <v>630</v>
+        <v>509</v>
       </c>
       <c r="H37" t="n">
-        <v>6661.87</v>
+        <v>2670.16</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3972,16 +3972,16 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>630</v>
+        <v>509</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46197.73806712963</v>
+        <v>46196.4912962963</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="M37" t="n">
-        <v>1181.63</v>
+        <v>1427.34</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31862</v>
+        <v>15473</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4049,17 +4049,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2607032</t>
+          <t>2606676</t>
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>46195</v>
+        <v>46190</v>
       </c>
       <c r="G38" t="n">
-        <v>1240</v>
+        <v>2390</v>
       </c>
       <c r="H38" t="n">
-        <v>13963.79</v>
+        <v>27531.01</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4067,16 +4067,16 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1240</v>
+        <v>2390</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46197.74751157407</v>
+        <v>46216.59604166666</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46201</v>
+        <v>46221</v>
       </c>
       <c r="M38" t="n">
-        <v>1474.21</v>
+        <v>3121.19</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4098,11 +4098,11 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1180/26</t>
+          <t>1216/26</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>46217</v>
+        <v>46225</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4125,11 +4125,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>27408</v>
+        <v>30909</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4139,65 +4139,65 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2607070</t>
+          <t>2606677</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>46197</v>
+        <v>46190</v>
       </c>
       <c r="G39" t="n">
-        <v>2301</v>
+        <v>1428</v>
       </c>
       <c r="H39" t="n">
-        <v>13575.9</v>
+        <v>14550.86</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>2365</v>
+        <v>1428</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46197.37570601852</v>
+        <v>46216.59912037037</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>46201</v>
+        <v>46218</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2688.64</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>27529.40</t>
+          <t>1216/26</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4220,11 +4220,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3119</v>
+        <v>17409</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4234,65 +4234,65 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2607069</t>
+          <t>2607032</t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>46197</v>
+        <v>46195</v>
       </c>
       <c r="G40" t="n">
-        <v>2365</v>
+        <v>1240</v>
       </c>
       <c r="H40" t="n">
-        <v>13953.5</v>
+        <v>13963.79</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2301</v>
+        <v>1240</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46197.37570601852</v>
+        <v>46197.74751157407</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>46201</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1474.21</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>27529.40</t>
+          <t>1180/26</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>46212</v>
+        <v>46217</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4315,11 +4315,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>17669</v>
+        <v>16600</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4329,65 +4329,65 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2607448</t>
+          <t>2607031</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G41" t="n">
+        <v>630</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6661.87</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>630</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>46197.73806712963</v>
+      </c>
+      <c r="L41" s="1" t="n">
         <v>46204</v>
       </c>
-      <c r="G41" t="n">
-        <v>1450</v>
-      </c>
-      <c r="H41" t="n">
-        <v>9526.5</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>MGKFL</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>1450</v>
-      </c>
-      <c r="K41" s="1" t="n">
-        <v>46205.38795138889</v>
-      </c>
-      <c r="L41" s="1" t="n">
-        <v>46216</v>
-      </c>
       <c r="M41" t="n">
-        <v>1058.5</v>
+        <v>1181.63</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>21370.50</t>
+          <t>1174/26</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>46222</v>
+        <v>46212</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>19313</v>
+        <v>10050</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4505,11 +4505,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>29251</v>
+        <v>9565</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4519,65 +4519,65 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2607546</t>
+          <t>2607448</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="G43" t="n">
-        <v>400</v>
+        <v>1450</v>
       </c>
       <c r="H43" t="n">
-        <v>2350</v>
+        <v>9526.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>400</v>
+        <v>1450</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46219.46043981481</v>
+        <v>46205.38795138889</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1058.5</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1296/26</t>
+          <t>21370.50</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>46237</v>
+        <v>46222</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8933</v>
+        <v>36679</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4695,11 +4695,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3550</v>
+        <v>34715</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4709,65 +4709,65 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2607651</t>
+          <t>2607546</t>
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46208</v>
+        <v>46205</v>
       </c>
       <c r="G45" t="n">
-        <v>8524</v>
+        <v>400</v>
       </c>
       <c r="H45" t="n">
-        <v>52818.8</v>
+        <v>2350</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>8524</v>
+        <v>400</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46208.38284722222</v>
+        <v>46219.46043981481</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="M45" t="n">
-        <v>9406.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>52818.82</t>
+          <t>1296/26</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>46229</v>
+        <v>46237</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5257</v>
+        <v>4174</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4804,22 +4804,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2607687</t>
+          <t>2607651</t>
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="G46" t="n">
-        <v>7980</v>
+        <v>8524</v>
       </c>
       <c r="H46" t="n">
-        <v>35504.62</v>
+        <v>52818.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4827,16 +4827,16 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>7980</v>
+        <v>8524</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46210</v>
+        <v>46208.38284722222</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="M46" t="n">
-        <v>724.58</v>
+        <v>9406.4</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4858,11 +4858,11 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>71178.31</t>
+          <t>52818.82</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>46238</v>
+        <v>46229</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>11329</v>
+        <v>1813</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4904,17 +4904,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2607865</t>
+          <t>2607687</t>
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46215</v>
+        <v>46209</v>
       </c>
       <c r="G47" t="n">
-        <v>8018</v>
+        <v>7980</v>
       </c>
       <c r="H47" t="n">
-        <v>35673.69</v>
+        <v>35504.62</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4922,16 +4922,16 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>8018</v>
+        <v>7980</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46215.36673611111</v>
+        <v>46210</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
       <c r="M47" t="n">
-        <v>728.03</v>
+        <v>724.58</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4249</v>
+        <v>21676</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ZXY</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2608096</t>
+          <t>2607865</t>
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46221</v>
+        <v>46215</v>
       </c>
       <c r="G48" t="n">
-        <v>6585</v>
+        <v>8018</v>
       </c>
       <c r="H48" t="n">
-        <v>31923.55</v>
+        <v>35673.69</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5017,28 +5017,28 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>6585</v>
+        <v>8018</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46252.40251157407</v>
+        <v>46215.36673611111</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>46275</v>
+        <v>46224</v>
       </c>
       <c r="M48" t="n">
-        <v>19566.05</v>
+        <v>728.03</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>3323/2026/2026090200147398</t>
+          <t>71178.31</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>46271</v>
+        <v>46238</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2642</v>
+        <v>31551</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5094,17 +5094,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2608097</t>
+          <t>2608096</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="G49" t="n">
-        <v>4788</v>
+        <v>6585</v>
       </c>
       <c r="H49" t="n">
-        <v>21523.18</v>
+        <v>31923.55</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5112,16 +5112,16 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>4788</v>
+        <v>6585</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46258.46469907407</v>
+        <v>46252.40251157407</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>46262</v>
+        <v>46275</v>
       </c>
       <c r="M49" t="n">
-        <v>13191.62</v>
+        <v>19566.05</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -5170,7 +5170,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>34930</v>
+        <v>30705</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5184,22 +5184,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2608253</t>
+          <t>2608097</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46222</v>
+        <v>46221</v>
       </c>
       <c r="G50" t="n">
-        <v>8241</v>
+        <v>4788</v>
       </c>
       <c r="H50" t="n">
-        <v>58956.11</v>
+        <v>21523.18</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5207,28 +5207,28 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>8241</v>
+        <v>4788</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46222.40752314815</v>
+        <v>46258.46469907407</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>46232</v>
+        <v>46262</v>
       </c>
       <c r="M50" t="n">
-        <v>1203.19</v>
+        <v>13191.62</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -5238,11 +5238,11 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>58956.11</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>46245</v>
+        <v>46271</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1350</v>
+        <v>13571</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5279,22 +5279,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2608524</t>
+          <t>2608253</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46229</v>
+        <v>46222</v>
       </c>
       <c r="G51" t="n">
-        <v>4973</v>
+        <v>8241</v>
       </c>
       <c r="H51" t="n">
-        <v>31329.9</v>
+        <v>58956.11</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5302,16 +5302,16 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>4973</v>
+        <v>8241</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46229.45681712963</v>
+        <v>46222.40752314815</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1203.19</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>40,868.10</t>
+          <t>58956.11</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -5360,7 +5360,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>39707</v>
+        <v>28874</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5374,22 +5374,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TMS Fashion (HK) Ltd.</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2608641</t>
+          <t>2608524</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
         <v>46229</v>
       </c>
       <c r="G52" t="n">
-        <v>2000</v>
+        <v>4973</v>
       </c>
       <c r="H52" t="n">
-        <v>13400</v>
+        <v>31329.9</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>2000</v>
+        <v>4973</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46246.47179398148</v>
+        <v>46229.45681712963</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>46263</v>
+        <v>46238</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5428,11 +5428,11 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>73197.90</t>
+          <t>40,868.10</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>46274</v>
+        <v>46245</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4521</v>
+        <v>4402</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5469,22 +5469,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TMS Fashion (HK) Ltd.</t>
+          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2608642</t>
+          <t>2608649</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="G53" t="n">
-        <v>1240</v>
+        <v>274</v>
       </c>
       <c r="H53" t="n">
-        <v>8308</v>
+        <v>1726.2</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5492,13 +5492,13 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1240</v>
+        <v>274</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46246.47179398148</v>
+        <v>46230.43035879629</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>46263</v>
+        <v>46238</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -5523,11 +5523,11 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>73197.90</t>
+          <t>40,868.10</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>46274</v>
+        <v>46245</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2361</v>
+        <v>28096</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5564,22 +5564,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>s.Oliver Bernd Freier GmbH  and  Co.KG</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2608649</t>
+          <t>2608653</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
         <v>46230</v>
       </c>
       <c r="G54" t="n">
-        <v>274</v>
+        <v>1920</v>
       </c>
       <c r="H54" t="n">
-        <v>1726.2</v>
+        <v>12384</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>274</v>
+        <v>1920</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46230.43035879629</v>
+        <v>46261.43150462963</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>46238</v>
+        <v>46266</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -5618,11 +5618,11 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>40,868.10</t>
+          <t>69327.7</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>46245</v>
+        <v>46281</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>42544</v>
+        <v>25151</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5740,11 +5740,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>8172</v>
+        <v>36728</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5754,36 +5754,36 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2608677</t>
+          <t>2608656</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="G56" t="n">
-        <v>405</v>
+        <v>4164</v>
       </c>
       <c r="H56" t="n">
-        <v>2389.5</v>
+        <v>27690.6</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>405</v>
+        <v>4164</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46236.65753472222</v>
+        <v>46254.40956018519</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -5793,26 +5793,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1390/26</t>
+          <t>69327.7</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>46261</v>
+        <v>46281</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5835,11 +5835,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>31953</v>
+        <v>12663</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5849,36 +5849,36 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2608678</t>
+          <t>2608655</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="G57" t="n">
-        <v>262</v>
+        <v>1450</v>
       </c>
       <c r="H57" t="n">
-        <v>1545.8</v>
+        <v>9352.5</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>262</v>
+        <v>1450</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46237.66037037037</v>
+        <v>46261.43150462963</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>46240</v>
+        <v>46263</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -5893,21 +5893,21 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1390/26</t>
+          <t>69327.7</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>46261</v>
+        <v>46281</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5930,11 +5930,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20166</v>
+        <v>25438</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5944,36 +5944,36 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2609047</t>
+          <t>2608654</t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46243</v>
+        <v>46230</v>
       </c>
       <c r="G58" t="n">
-        <v>10106</v>
+        <v>808</v>
       </c>
       <c r="H58" t="n">
-        <v>66742.45</v>
+        <v>5211.6</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>10106</v>
+        <v>808</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46243.43114583333</v>
+        <v>46261.43150462963</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>46250</v>
+        <v>46263</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -5983,26 +5983,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1390/26</t>
+          <t>69327.7</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>46261</v>
+        <v>46281</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>6361</v>
+        <v>27316</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6044,17 +6044,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2609048</t>
+          <t>2608678</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46243</v>
+        <v>46231</v>
       </c>
       <c r="G59" t="n">
-        <v>418</v>
+        <v>262</v>
       </c>
       <c r="H59" t="n">
-        <v>2766.2</v>
+        <v>1545.8</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6062,13 +6062,13 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>418</v>
+        <v>262</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46243.42872685185</v>
+        <v>46237.66037037037</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>46253</v>
+        <v>46240</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -6120,11 +6120,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>22108</v>
+        <v>37713</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6134,39 +6134,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2609112</t>
+          <t>2608677</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46243</v>
+        <v>46231</v>
       </c>
       <c r="G60" t="n">
-        <v>5852</v>
+        <v>405</v>
       </c>
       <c r="H60" t="n">
-        <v>26036.72</v>
+        <v>2389.5</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>5852</v>
+        <v>405</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46243.42559027778</v>
+        <v>46236.65753472222</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>46253</v>
+        <v>46250</v>
       </c>
       <c r="M60" t="n">
-        <v>531.36</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -6178,21 +6178,21 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>84872.08</t>
+          <t>1390/26</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>46268</v>
+        <v>46261</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6215,11 +6215,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>25768</v>
+        <v>23083</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6229,65 +6229,65 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ZXY</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2609270</t>
+          <t>2609048</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46247</v>
+        <v>46243</v>
       </c>
       <c r="G61" t="n">
-        <v>1882</v>
+        <v>418</v>
       </c>
       <c r="H61" t="n">
-        <v>8124.6</v>
+        <v>2766.2</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1882</v>
+        <v>418</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46247.51739583333</v>
+        <v>46243.42872685185</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="M61" t="n">
-        <v>5416.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>3323/2026/2026090200147398</t>
+          <t>1390/26</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>46271</v>
+        <v>46261</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>15585</v>
+        <v>7297</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6329,17 +6329,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2609284</t>
+          <t>2609112</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46250</v>
+        <v>46243</v>
       </c>
       <c r="G62" t="n">
-        <v>2000</v>
+        <v>5852</v>
       </c>
       <c r="H62" t="n">
-        <v>14308</v>
+        <v>26036.72</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -6347,16 +6347,16 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>2000</v>
+        <v>5852</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46250.38284722222</v>
+        <v>46243.42559027778</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>46264</v>
+        <v>46253</v>
       </c>
       <c r="M62" t="n">
-        <v>292</v>
+        <v>531.36</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -6405,11 +6405,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>13030</v>
+        <v>25243</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MGKFL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6419,39 +6419,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>DK Company</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2609283</t>
+          <t>2609047</t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G63" t="n">
+        <v>10106</v>
+      </c>
+      <c r="H63" t="n">
+        <v>66742.45</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>10106</v>
+      </c>
+      <c r="K63" s="1" t="n">
+        <v>46243.43114583333</v>
+      </c>
+      <c r="L63" s="1" t="n">
         <v>46250</v>
       </c>
-      <c r="G63" t="n">
-        <v>6612</v>
-      </c>
-      <c r="H63" t="n">
-        <v>29418.11</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>MGKFL</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>6612</v>
-      </c>
-      <c r="K63" s="1" t="n">
-        <v>46250.38120370371</v>
-      </c>
-      <c r="L63" s="1" t="n">
-        <v>46264</v>
-      </c>
       <c r="M63" t="n">
-        <v>600.37</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -6463,21 +6463,21 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>DBBL</t>
+          <t>PRM</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>84872.08</t>
+          <t>1390/26</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>46268</v>
+        <v>46261</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>36958</v>
+        <v>22628</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6514,22 +6514,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2609285</t>
+          <t>2609270</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="G64" t="n">
-        <v>2112</v>
+        <v>1882</v>
       </c>
       <c r="H64" t="n">
-        <v>15109.25</v>
+        <v>8124.6</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6537,28 +6537,28 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>2112</v>
+        <v>1882</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46250.38284722222</v>
+        <v>46247.51739583333</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>46264</v>
+        <v>46252</v>
       </c>
       <c r="M64" t="n">
-        <v>308.35</v>
+        <v>5416.4</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>84872.08</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1733</v>
+        <v>21931</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TMS Fashion (HK) Ltd.</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2609418</t>
+          <t>2609284</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="G65" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H65" t="n">
-        <v>9240</v>
+        <v>14308</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -6632,16 +6632,16 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46259.45524305556</v>
+        <v>46250.38284722222</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6663,11 +6663,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>73197.90</t>
+          <t>84872.08</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>585</v>
+        <v>41271</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6704,22 +6704,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TMS Fashion (HK) Ltd.</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2609419</t>
+          <t>2609285</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="G66" t="n">
-        <v>5487</v>
+        <v>2112</v>
       </c>
       <c r="H66" t="n">
-        <v>42249.9</v>
+        <v>15109.25</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -6727,16 +6727,16 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>5487</v>
+        <v>2112</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46259.45524305556</v>
+        <v>46250.38284722222</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>308.35</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6758,11 +6758,11 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>73197.90</t>
+          <t>84872.08</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>22485</v>
+        <v>20754</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -6799,22 +6799,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ZXY</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2609438</t>
+          <t>2609283</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46252</v>
+        <v>46250</v>
       </c>
       <c r="G67" t="n">
-        <v>8334</v>
+        <v>6612</v>
       </c>
       <c r="H67" t="n">
-        <v>33705.8</v>
+        <v>29418.11</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -6822,28 +6822,28 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>8334</v>
+        <v>6612</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46252.40453703704</v>
+        <v>46250.38120370371</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>46256</v>
+        <v>46264</v>
       </c>
       <c r="M67" t="n">
-        <v>20658.4</v>
+        <v>600.37</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6853,11 +6853,11 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>3323/2026/2026090200147398</t>
+          <t>84872.08</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>46271</v>
+        <v>46268</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>18477</v>
+        <v>17362</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -6899,17 +6899,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2609878</t>
+          <t>2609417</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46264</v>
+        <v>46251</v>
       </c>
       <c r="G68" t="n">
-        <v>900</v>
+        <v>785</v>
       </c>
       <c r="H68" t="n">
-        <v>6300</v>
+        <v>5809</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>900</v>
+        <v>785</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46274.64322916666</v>
+        <v>46264.54070601852</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>46283</v>
+        <v>46263</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6948,11 +6948,11 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>132895</t>
+          <t>69327.7</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>37371</v>
+        <v>22909</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -6994,17 +6994,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2609877</t>
+          <t>2609416</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46264</v>
+        <v>46251</v>
       </c>
       <c r="G69" t="n">
-        <v>2368</v>
+        <v>1200</v>
       </c>
       <c r="H69" t="n">
-        <v>16576</v>
+        <v>8880</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>2368</v>
+        <v>1200</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46274.64322916666</v>
+        <v>46264.54070601852</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>46283</v>
+        <v>46265</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7043,11 +7043,11 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>132895</t>
+          <t>69327.7</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>7738</v>
+        <v>39488</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -7084,22 +7084,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TMS Fashion (HK) Ltd.</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2609879</t>
+          <t>2609438</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46264</v>
+        <v>46252</v>
       </c>
       <c r="G70" t="n">
-        <v>15717</v>
+        <v>8334</v>
       </c>
       <c r="H70" t="n">
-        <v>110019</v>
+        <v>33705.8</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -7107,28 +7107,28 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>15717</v>
+        <v>8334</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46274.64322916666</v>
+        <v>46252.40453703704</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>46283</v>
+        <v>46256</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>20658.4</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -7138,11 +7138,11 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>132895</t>
+          <t>3323/2026/2026090200147398</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>46288</v>
+        <v>46271</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>21027</v>
+        <v>13307</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -7179,22 +7179,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Matalan</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2610178</t>
+          <t>2609878</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="G71" t="n">
-        <v>10982</v>
+        <v>900</v>
       </c>
       <c r="H71" t="n">
-        <v>48861.11</v>
+        <v>6300</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7202,16 +7202,16 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>10982</v>
+        <v>900</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46271.53631944444</v>
+        <v>46274.64322916666</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>46285</v>
+        <v>46283</v>
       </c>
       <c r="M71" t="n">
-        <v>997.17</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>52958.59</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7260,11 +7260,11 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>41520</v>
+        <v>10724</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7274,39 +7274,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2610184</t>
+          <t>2609879</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46273</v>
+        <v>46264</v>
       </c>
       <c r="G72" t="n">
-        <v>1635</v>
+        <v>15717</v>
       </c>
       <c r="H72" t="n">
-        <v>7708.95</v>
+        <v>110019</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>1635</v>
+        <v>15717</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46272.45939814814</v>
+        <v>46274.64322916666</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="M72" t="n">
-        <v>1492.4</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -7318,21 +7318,21 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>43695.75</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7355,11 +7355,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>22215</v>
+        <v>35506</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7369,39 +7369,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>TMS Fashion (HK) Ltd.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2610183</t>
+          <t>2609877</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46273</v>
+        <v>46264</v>
       </c>
       <c r="G73" t="n">
-        <v>5167</v>
+        <v>2368</v>
       </c>
       <c r="H73" t="n">
-        <v>23295.9</v>
+        <v>16576</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>5167</v>
+        <v>2368</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46272.46409722222</v>
+        <v>46274.64322916666</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="M73" t="n">
-        <v>7430.4</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -7413,21 +7413,21 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>43695.75</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7450,11 +7450,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20721</v>
+        <v>32182</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7464,39 +7464,39 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Best Seller</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2610275</t>
+          <t>2610003</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2952</v>
+      </c>
+      <c r="H74" t="n">
+        <v>16850.34</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>2952</v>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>46266.41614583333</v>
+      </c>
+      <c r="L74" s="1" t="n">
         <v>46275</v>
       </c>
-      <c r="G74" t="n">
-        <v>1052</v>
-      </c>
-      <c r="H74" t="n">
-        <v>9792.1</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>1052</v>
-      </c>
-      <c r="K74" s="1" t="n">
-        <v>46275.37585648148</v>
-      </c>
-      <c r="L74" s="1" t="n">
-        <v>46282</v>
-      </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>886.86</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -7513,16 +7513,16 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>43695.75</t>
+          <t>16850.34</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7545,11 +7545,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>15300</v>
+        <v>17986</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7559,39 +7559,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DK Company</t>
+          <t>Matalan</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2610276</t>
+          <t>2610178</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46275</v>
+        <v>46271</v>
       </c>
       <c r="G75" t="n">
-        <v>300</v>
+        <v>10982</v>
       </c>
       <c r="H75" t="n">
-        <v>2898.8</v>
+        <v>48861.11</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGKFL</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>300</v>
+        <v>10982</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46275.37873842593</v>
+        <v>46271.53631944444</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>997.17</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -7603,21 +7603,21 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PRM</t>
+          <t>DBBL</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>43695.75</t>
+          <t>52958.59</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7633,6 +7633,671 @@
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1798</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DK Company</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2610184</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1635</v>
+      </c>
+      <c r="H76" t="n">
+        <v>7708.95</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1635</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>46272.45939814814</v>
+      </c>
+      <c r="L76" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1492.4</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>PRM</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1526/2026</t>
+        </is>
+      </c>
+      <c r="S76" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>23904</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DK Company</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2610183</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5167</v>
+      </c>
+      <c r="H77" t="n">
+        <v>23295.91</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>5167</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>46272.46409722222</v>
+      </c>
+      <c r="L77" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="M77" t="n">
+        <v>7430.39</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>PRM</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1526/2026</t>
+        </is>
+      </c>
+      <c r="S77" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>28127</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DK Company</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2610275</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1052</v>
+      </c>
+      <c r="H78" t="n">
+        <v>9792.1</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1052</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>46275.37585648148</v>
+      </c>
+      <c r="L78" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>PRM</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1526/2026</t>
+        </is>
+      </c>
+      <c r="S78" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>33573</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DK Company</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2610276</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="G79" t="n">
+        <v>300</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2898.8</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>300</v>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>46275.37873842593</v>
+      </c>
+      <c r="L79" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>PRM</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1526/2026</t>
+        </is>
+      </c>
+      <c r="S79" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>41393</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Matalan</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2610349</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="G80" t="n">
+        <v>20924</v>
+      </c>
+      <c r="H80" t="n">
+        <v>101194.06</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>20924</v>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>46278.46532407407</v>
+      </c>
+      <c r="L80" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2065.18</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>DBBL</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>104482.55</t>
+        </is>
+      </c>
+      <c r="S80" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>15417</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Matalan</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2610403</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="G81" t="n">
+        <v>680</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3288.49</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>680</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>46278.46532407407</v>
+      </c>
+      <c r="L81" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M81" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Jabel-Ali</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>DBBL</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>104482.55</t>
+        </is>
+      </c>
+      <c r="S81" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>20046</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sweater</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Matalan</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2610618</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="G82" t="n">
+        <v>13596</v>
+      </c>
+      <c r="H82" t="n">
+        <v>69283.45</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>MGKFL</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>13596</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>46284.65298611111</v>
+      </c>
+      <c r="L82" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1413.95</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>DBBL</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>69283.45</t>
+        </is>
+      </c>
+      <c r="S82" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr">
         <is>
           <t>No</t>
         </is>
